--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484078_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484078_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.7484</v>
+        <v>6.5622</v>
       </c>
       <c r="E2" t="n">
-        <v>5.2918</v>
+        <v>5.1898</v>
       </c>
       <c r="F2" t="n">
-        <v>1.4566</v>
+        <v>1.3724</v>
       </c>
       <c r="G2" t="n">
         <v>5.697</v>
@@ -610,13 +610,13 @@
         <v>2.1822</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.1161</v>
+        <v>-1.3023</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.255</v>
+        <v>-0.357</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.8611</v>
+        <v>-0.9453</v>
       </c>
       <c r="V2" t="n">
         <v>4.1513</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>R. DIAZ SANCHEZ</t>
+          <t>M. PUIG DE GRACIA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,40 +643,40 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.8091</v>
+        <v>4.6626</v>
       </c>
       <c r="E3" t="n">
-        <v>3.0842</v>
+        <v>1.9692</v>
       </c>
       <c r="F3" t="n">
-        <v>1.7249</v>
+        <v>2.6935</v>
       </c>
       <c r="G3" t="n">
-        <v>6.15</v>
+        <v>6.1856</v>
       </c>
       <c r="H3" t="n">
-        <v>1.2645</v>
+        <v>1.7186</v>
       </c>
       <c r="I3" t="n">
-        <v>4.8856</v>
+        <v>4.467</v>
       </c>
       <c r="J3" t="n">
-        <v>4.2064</v>
+        <v>3.2274</v>
       </c>
       <c r="K3" t="n">
-        <v>0.4287</v>
+        <v>0.8075</v>
       </c>
       <c r="L3" t="n">
-        <v>3.7777</v>
+        <v>2.4199</v>
       </c>
       <c r="M3" t="n">
-        <v>1.9436</v>
+        <v>2.9582</v>
       </c>
       <c r="N3" t="n">
-        <v>0.8358</v>
+        <v>0.9111</v>
       </c>
       <c r="O3" t="n">
-        <v>1.1078</v>
+        <v>2.0471</v>
       </c>
       <c r="P3" t="n">
         <v>0.5952</v>
@@ -688,28 +688,28 @@
         <v>1.7855</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.7296</v>
+        <v>-1.5149</v>
       </c>
       <c r="T3" t="n">
-        <v>0.06809999999999999</v>
+        <v>-0.0679</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.7977</v>
+        <v>-1.4469</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.2065</v>
+        <v>-0.6032</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.2065</v>
+        <v>-0.6032</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. PUIG DE GRACIA</t>
+          <t>R. DIAZ SANCHEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,40 +721,40 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.8337</v>
+        <v>4.1485</v>
       </c>
       <c r="E4" t="n">
-        <v>1.561</v>
+        <v>2.6761</v>
       </c>
       <c r="F4" t="n">
-        <v>2.2727</v>
+        <v>1.4724</v>
       </c>
       <c r="G4" t="n">
-        <v>6.1856</v>
+        <v>6.15</v>
       </c>
       <c r="H4" t="n">
-        <v>1.7186</v>
+        <v>1.2645</v>
       </c>
       <c r="I4" t="n">
-        <v>4.467</v>
+        <v>4.8856</v>
       </c>
       <c r="J4" t="n">
-        <v>3.2274</v>
+        <v>4.2064</v>
       </c>
       <c r="K4" t="n">
-        <v>0.8075</v>
+        <v>0.4287</v>
       </c>
       <c r="L4" t="n">
-        <v>2.4199</v>
+        <v>3.7777</v>
       </c>
       <c r="M4" t="n">
-        <v>2.9582</v>
+        <v>1.9436</v>
       </c>
       <c r="N4" t="n">
-        <v>0.9111</v>
+        <v>0.8358</v>
       </c>
       <c r="O4" t="n">
-        <v>2.0471</v>
+        <v>1.1078</v>
       </c>
       <c r="P4" t="n">
         <v>0.5952</v>
@@ -766,22 +766,22 @@
         <v>1.7855</v>
       </c>
       <c r="S4" t="n">
-        <v>-2.3438</v>
+        <v>-1.3902</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.4761</v>
+        <v>-0.34</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.8678</v>
+        <v>-1.0502</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.6032</v>
+        <v>-1.2065</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.6032</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.7193</v>
+        <v>2.5713</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.06279999999999999</v>
+        <v>-0.2669</v>
       </c>
       <c r="F5" t="n">
-        <v>2.7821</v>
+        <v>2.8382</v>
       </c>
       <c r="G5" t="n">
         <v>2.9483</v>
@@ -844,13 +844,13 @@
         <v>2.579</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.4671</v>
+        <v>-0.615</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1928</v>
+        <v>-0.0113</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.6599</v>
+        <v>-0.6038</v>
       </c>
       <c r="V5" t="n">
         <v>-1.349</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. MONTALVO PEREZ</t>
+          <t>P. SANTIAGO PAZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.354</v>
+        <v>2.0814</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7413999999999999</v>
+        <v>0.1175</v>
       </c>
       <c r="F6" t="n">
-        <v>1.6126</v>
+        <v>1.9639</v>
       </c>
       <c r="G6" t="n">
-        <v>1.1556</v>
+        <v>2.4966</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6853</v>
+        <v>1.854</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4703</v>
+        <v>0.6425999999999999</v>
       </c>
       <c r="J6" t="n">
-        <v>1.3935</v>
+        <v>1.6988</v>
       </c>
       <c r="K6" t="n">
-        <v>0.6706</v>
+        <v>0.4085</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7229</v>
+        <v>1.2903</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.2379</v>
+        <v>0.7978</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0147</v>
+        <v>1.4455</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.2526</v>
+        <v>-0.6477000000000001</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.5952</v>
+        <v>0.1984</v>
       </c>
       <c r="Q6" t="n">
         <v>-1.9838</v>
       </c>
       <c r="R6" t="n">
-        <v>1.3887</v>
+        <v>2.1822</v>
       </c>
       <c r="S6" t="n">
-        <v>2.202</v>
+        <v>-0.6136</v>
       </c>
       <c r="T6" t="n">
-        <v>1.7402</v>
+        <v>0.4025</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4618</v>
+        <v>-1.0161</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.4085</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.4085</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. QUIROS LOPEZ</t>
+          <t>J. GAVALDA GUILLEN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.4278</v>
+        <v>1.4464</v>
       </c>
       <c r="E7" t="n">
-        <v>1.6104</v>
+        <v>1.8556</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.1826</v>
+        <v>-0.4092</v>
       </c>
       <c r="G7" t="n">
-        <v>2.0405</v>
+        <v>2.1343</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2163</v>
+        <v>-0.4491</v>
       </c>
       <c r="I7" t="n">
-        <v>1.8242</v>
+        <v>2.5833</v>
       </c>
       <c r="J7" t="n">
-        <v>1.854</v>
+        <v>1.3511</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3279</v>
+        <v>-0.5391</v>
       </c>
       <c r="L7" t="n">
-        <v>1.5261</v>
+        <v>1.8901</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1865</v>
+        <v>0.7832</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.1116</v>
+        <v>0.09</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2981</v>
+        <v>0.6932</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.5952</v>
+        <v>0.5952</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.1903</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
         <v>0.5952</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0176</v>
+        <v>-0.0765</v>
       </c>
       <c r="T7" t="n">
-        <v>0.9467</v>
+        <v>0.5044999999999999</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.9643</v>
+        <v>-0.5810999999999999</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-1.2065</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. GAVALDA GUILLEN</t>
+          <t>P. MARRÓN ROSA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.0639</v>
+        <v>1.1416</v>
       </c>
       <c r="E8" t="n">
-        <v>1.7536</v>
+        <v>-1.2223</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.6897</v>
+        <v>2.3639</v>
       </c>
       <c r="G8" t="n">
-        <v>2.1343</v>
+        <v>2.4901</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.4491</v>
+        <v>1.2852</v>
       </c>
       <c r="I8" t="n">
-        <v>2.5833</v>
+        <v>1.2048</v>
       </c>
       <c r="J8" t="n">
-        <v>1.3511</v>
+        <v>1.1676</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.5391</v>
+        <v>1.2001</v>
       </c>
       <c r="L8" t="n">
-        <v>1.8901</v>
+        <v>-0.0325</v>
       </c>
       <c r="M8" t="n">
-        <v>0.7832</v>
+        <v>1.3225</v>
       </c>
       <c r="N8" t="n">
-        <v>0.09</v>
+        <v>0.0851</v>
       </c>
       <c r="O8" t="n">
-        <v>0.6932</v>
+        <v>1.2374</v>
       </c>
       <c r="P8" t="n">
-        <v>0.5952</v>
+        <v>-1.5871</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-3.1741</v>
       </c>
       <c r="R8" t="n">
-        <v>0.5952</v>
+        <v>1.5871</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4591</v>
+        <v>-0.6306</v>
       </c>
       <c r="T8" t="n">
-        <v>0.4025</v>
+        <v>-0.08500000000000001</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.8616</v>
+        <v>-0.5457</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.2065</v>
+        <v>0.8692</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.8692</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.2065</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>P. MARRÓN ROSA</t>
+          <t>A. QUIROS LOPEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9656</v>
+        <v>1.1038</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.4263</v>
+        <v>1.2023</v>
       </c>
       <c r="F9" t="n">
-        <v>2.3919</v>
+        <v>-0.0985</v>
       </c>
       <c r="G9" t="n">
-        <v>2.4901</v>
+        <v>2.0405</v>
       </c>
       <c r="H9" t="n">
-        <v>1.2852</v>
+        <v>0.2163</v>
       </c>
       <c r="I9" t="n">
-        <v>1.2048</v>
+        <v>1.8242</v>
       </c>
       <c r="J9" t="n">
-        <v>1.1676</v>
+        <v>1.854</v>
       </c>
       <c r="K9" t="n">
-        <v>1.2001</v>
+        <v>0.3279</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.0325</v>
+        <v>1.5261</v>
       </c>
       <c r="M9" t="n">
-        <v>1.3225</v>
+        <v>0.1865</v>
       </c>
       <c r="N9" t="n">
-        <v>0.0851</v>
+        <v>-0.1116</v>
       </c>
       <c r="O9" t="n">
-        <v>1.2374</v>
+        <v>0.2981</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.5871</v>
+        <v>-0.5952</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.1741</v>
+        <v>-1.1903</v>
       </c>
       <c r="R9" t="n">
-        <v>1.5871</v>
+        <v>0.5952</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.8066</v>
+        <v>-0.3415</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.289</v>
+        <v>0.5386</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.5175999999999999</v>
+        <v>-0.8801</v>
       </c>
       <c r="V9" t="n">
-        <v>0.8692</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0.8692</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>P. SANTIAGO PAZ</t>
+          <t>A. MONTALVO PEREZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9566</v>
+        <v>0.9129</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.6988</v>
+        <v>-0.2789</v>
       </c>
       <c r="F10" t="n">
-        <v>1.6553</v>
+        <v>1.1918</v>
       </c>
       <c r="G10" t="n">
-        <v>2.4966</v>
+        <v>1.1556</v>
       </c>
       <c r="H10" t="n">
-        <v>1.854</v>
+        <v>0.6853</v>
       </c>
       <c r="I10" t="n">
-        <v>0.6425999999999999</v>
+        <v>0.4703</v>
       </c>
       <c r="J10" t="n">
-        <v>1.6988</v>
+        <v>1.3935</v>
       </c>
       <c r="K10" t="n">
-        <v>0.4085</v>
+        <v>0.6706</v>
       </c>
       <c r="L10" t="n">
-        <v>1.2903</v>
+        <v>0.7229</v>
       </c>
       <c r="M10" t="n">
-        <v>0.7978</v>
+        <v>-0.2379</v>
       </c>
       <c r="N10" t="n">
-        <v>1.4455</v>
+        <v>0.0147</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.6477000000000001</v>
+        <v>-0.2526</v>
       </c>
       <c r="P10" t="n">
-        <v>0.1984</v>
+        <v>-0.5952</v>
       </c>
       <c r="Q10" t="n">
         <v>-1.9838</v>
       </c>
       <c r="R10" t="n">
-        <v>2.1822</v>
+        <v>1.3887</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.7385</v>
+        <v>0.7609</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4137</v>
+        <v>0.7199</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.3247</v>
+        <v>0.041</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-0.4085</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>-0.4085</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0543</v>
+        <v>0.0518</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.0129</v>
+        <v>0.2932</v>
       </c>
       <c r="F11" t="n">
-        <v>0.06710000000000001</v>
+        <v>-0.2415</v>
       </c>
       <c r="G11" t="n">
         <v>-0.2897</v>
@@ -1312,13 +1312,13 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0.344</v>
+        <v>0.3415</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1133</v>
+        <v>0.1927</v>
       </c>
       <c r="U11" t="n">
-        <v>0.4574</v>
+        <v>0.1488</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.0811</v>
+        <v>-1.9969</v>
       </c>
       <c r="E12" t="n">
         <v>-1.5291</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.5518999999999999</v>
+        <v>-0.4678</v>
       </c>
       <c r="G12" t="n">
         <v>-1.9421</v>
@@ -1390,13 +1390,13 @@
         <v>0.7935</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.3293</v>
+        <v>-0.2451</v>
       </c>
       <c r="T12" t="n">
         <v>-0.2494</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0799</v>
+        <v>0.0042</v>
       </c>
       <c r="V12" t="n">
         <v>-0.6032</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.1996</v>
+        <v>-4.0338</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.1935</v>
+        <v>-2.8875</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.006</v>
+        <v>-1.1463</v>
       </c>
       <c r="G13" t="n">
         <v>-3.3408</v>
@@ -1468,13 +1468,13 @@
         <v>0.3968</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.2636</v>
+        <v>-0.0978</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.2494</v>
+        <v>0.0567</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.0142</v>
+        <v>-0.1545</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>18.652</v>
+        <v>18.6518</v>
       </c>
       <c r="E14" t="n">
-        <v>7.119000000000002</v>
+        <v>7.118999999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>11.533</v>
+        <v>11.5328</v>
       </c>
       <c r="G14" t="n">
         <v>25.7254</v>
@@ -1531,13 +1531,13 @@
         <v>6.577299999999999</v>
       </c>
       <c r="N14" t="n">
-        <v>6.317100000000001</v>
+        <v>6.317100000000002</v>
       </c>
       <c r="O14" t="n">
-        <v>0.2601000000000004</v>
+        <v>0.2600999999999996</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.9919000000000001</v>
+        <v>-0.9918999999999999</v>
       </c>
       <c r="Q14" t="n">
         <v>-16.8625</v>
@@ -1546,13 +1546,13 @@
         <v>15.8709</v>
       </c>
       <c r="S14" t="n">
-        <v>-5.7253</v>
+        <v>-5.7251</v>
       </c>
       <c r="T14" t="n">
-        <v>1.3044</v>
+        <v>1.3043</v>
       </c>
       <c r="U14" t="n">
-        <v>-7.029599999999999</v>
+        <v>-7.029699999999999</v>
       </c>
       <c r="V14" t="n">
         <v>-0.3563999999999999</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.3883</v>
+        <v>3.8925</v>
       </c>
       <c r="E15" t="n">
-        <v>4.8986</v>
+        <v>5.1026</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.5103</v>
+        <v>-1.2102</v>
       </c>
       <c r="G15" t="n">
         <v>-0.3985</v>
@@ -1624,13 +1624,13 @@
         <v>2.1822</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.344</v>
+        <v>0.1602</v>
       </c>
       <c r="T15" t="n">
-        <v>0.2382</v>
+        <v>0.4422</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.5822000000000001</v>
+        <v>-0.2821</v>
       </c>
       <c r="V15" t="n">
         <v>2.1469</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.4691</v>
+        <v>0.9649</v>
       </c>
       <c r="E16" t="n">
-        <v>1.197</v>
+        <v>0.5848</v>
       </c>
       <c r="F16" t="n">
-        <v>0.2721</v>
+        <v>0.38</v>
       </c>
       <c r="G16" t="n">
         <v>-1.2216</v>
@@ -1702,13 +1702,13 @@
         <v>0.7935</v>
       </c>
       <c r="S16" t="n">
-        <v>2.0956</v>
+        <v>1.5914</v>
       </c>
       <c r="T16" t="n">
-        <v>1.7629</v>
+        <v>1.1507</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3327</v>
+        <v>0.4407</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>P. LLABRES TUGORES</t>
+          <t>M. AGUILO RODRIGUEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.7754</v>
+        <v>-0.5286</v>
       </c>
       <c r="E17" t="n">
-        <v>1.0509</v>
+        <v>0.2709</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.2756</v>
+        <v>-0.7995</v>
       </c>
       <c r="G17" t="n">
-        <v>-3.6601</v>
+        <v>0.1378</v>
       </c>
       <c r="H17" t="n">
-        <v>-2.0355</v>
+        <v>-0.1006</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.6246</v>
+        <v>0.2384</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.8764</v>
+        <v>1.5806</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.4372</v>
+        <v>-0.3873</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.4392</v>
+        <v>1.9679</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.7836</v>
+        <v>-1.4428</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.5983</v>
+        <v>0.2867</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.1853</v>
+        <v>-1.7295</v>
       </c>
       <c r="P17" t="n">
-        <v>1.3887</v>
+        <v>-0.7935</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.1903</v>
+        <v>-1.9838</v>
       </c>
       <c r="R17" t="n">
-        <v>2.579</v>
+        <v>1.1903</v>
       </c>
       <c r="S17" t="n">
-        <v>3.4361</v>
+        <v>-0.1388</v>
       </c>
       <c r="T17" t="n">
-        <v>3.1177</v>
+        <v>0.4082</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3184</v>
+        <v>-0.547</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.3894</v>
+        <v>0.266</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.266</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.3894</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. AGUILO RODRIGUEZ</t>
+          <t>L. SANCHEZ MORENO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.6526999999999999</v>
+        <v>-0.5528999999999999</v>
       </c>
       <c r="E18" t="n">
-        <v>0.475</v>
+        <v>1.0441</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.1277</v>
+        <v>-1.597</v>
       </c>
       <c r="G18" t="n">
-        <v>0.1378</v>
+        <v>-0.3421</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.1006</v>
+        <v>-0.1464</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2384</v>
+        <v>-0.1957</v>
       </c>
       <c r="J18" t="n">
-        <v>1.5806</v>
+        <v>1.8431</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.3873</v>
+        <v>1.3911</v>
       </c>
       <c r="L18" t="n">
-        <v>1.9679</v>
+        <v>0.452</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.4428</v>
+        <v>-2.1853</v>
       </c>
       <c r="N18" t="n">
-        <v>0.2867</v>
+        <v>-1.5376</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.7295</v>
+        <v>-0.6477000000000001</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.7935</v>
+        <v>0.7935</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.9838</v>
+        <v>-1.3887</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1903</v>
+        <v>2.1822</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.263</v>
+        <v>1.4086</v>
       </c>
       <c r="T18" t="n">
-        <v>0.6122</v>
+        <v>0.5896</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.8752</v>
+        <v>0.819</v>
       </c>
       <c r="V18" t="n">
-        <v>0.266</v>
+        <v>-2.4129</v>
       </c>
       <c r="W18" t="n">
-        <v>0.266</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-2.4129</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.1124</v>
+        <v>-0.6244</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.9694</v>
+        <v>-2.5613</v>
       </c>
       <c r="F19" t="n">
-        <v>1.857</v>
+        <v>1.9369</v>
       </c>
       <c r="G19" t="n">
         <v>1.2461</v>
@@ -1936,13 +1936,13 @@
         <v>1.1903</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3945</v>
+        <v>0.0935</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4364</v>
+        <v>-0.0283</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0419</v>
+        <v>0.1218</v>
       </c>
       <c r="V19" t="n">
         <v>1.0118</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>L. SANCHEZ MORENO</t>
+          <t>P. LLABRES TUGORES</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.8368</v>
+        <v>-0.7874</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.3843</v>
+        <v>-0.4795</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.4525</v>
+        <v>-0.3079</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.3421</v>
+        <v>-3.6601</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.1464</v>
+        <v>-2.0355</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1957</v>
+        <v>-1.6246</v>
       </c>
       <c r="J20" t="n">
-        <v>1.8431</v>
+        <v>-0.8764</v>
       </c>
       <c r="K20" t="n">
-        <v>1.3911</v>
+        <v>-0.4372</v>
       </c>
       <c r="L20" t="n">
-        <v>0.452</v>
+        <v>-0.4392</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.1853</v>
+        <v>-2.7836</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.5376</v>
+        <v>-1.5983</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.6477000000000001</v>
+        <v>-1.1853</v>
       </c>
       <c r="P20" t="n">
-        <v>0.7935</v>
+        <v>1.3887</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.3887</v>
+        <v>-1.1903</v>
       </c>
       <c r="R20" t="n">
-        <v>2.1822</v>
+        <v>2.579</v>
       </c>
       <c r="S20" t="n">
-        <v>0.1247</v>
+        <v>1.8734</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.8388</v>
+        <v>1.5873</v>
       </c>
       <c r="U20" t="n">
-        <v>0.9635</v>
+        <v>0.2862</v>
       </c>
       <c r="V20" t="n">
-        <v>-2.4129</v>
+        <v>-0.3894</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-2.4129</v>
+        <v>-0.3894</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>T. LLOBERA BIBILONI</t>
+          <t>H. MORRO BALERA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,58 +2047,58 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.1923</v>
+        <v>-2.4183</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.8752</v>
+        <v>-2.5505</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.3171</v>
+        <v>0.1322</v>
       </c>
       <c r="G21" t="n">
-        <v>-4.4987</v>
+        <v>-3.2841</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.94</v>
+        <v>0.2269</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.5587</v>
+        <v>-3.511</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.9069</v>
+        <v>-2.3579</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.3498</v>
+        <v>-0.3173</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.5572</v>
+        <v>-2.0406</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.5918</v>
+        <v>-0.9263</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.5901999999999999</v>
+        <v>0.5442</v>
       </c>
       <c r="O21" t="n">
-        <v>-2.0016</v>
+        <v>-1.4704</v>
       </c>
       <c r="P21" t="n">
-        <v>1.3887</v>
+        <v>0.7935</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.1984</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.5871</v>
+        <v>0.7935</v>
       </c>
       <c r="S21" t="n">
-        <v>0.9177</v>
+        <v>0.0723</v>
       </c>
       <c r="T21" t="n">
-        <v>1.2301</v>
+        <v>-0.1927</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3124</v>
+        <v>0.265</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>C. POYATOS PARRA</t>
+          <t>T. LLOBERA BIBILONI</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.7738</v>
+        <v>-2.5843</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.2516</v>
+        <v>-1.4874</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.5222</v>
+        <v>-1.0969</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.752</v>
+        <v>-4.4987</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.2725</v>
+        <v>-1.94</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.4795</v>
+        <v>-2.5587</v>
       </c>
       <c r="J22" t="n">
-        <v>-2.5748</v>
+        <v>-1.9069</v>
       </c>
       <c r="K22" t="n">
-        <v>-2.0151</v>
+        <v>-1.3498</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.5597</v>
+        <v>-0.5572</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.1772</v>
+        <v>-2.5918</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.2574</v>
+        <v>-0.5901999999999999</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.9198</v>
+        <v>-2.0016</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>1.3887</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.1903</v>
+        <v>-0.1984</v>
       </c>
       <c r="R22" t="n">
-        <v>1.1903</v>
+        <v>1.5871</v>
       </c>
       <c r="S22" t="n">
-        <v>1.5815</v>
+        <v>0.5258</v>
       </c>
       <c r="T22" t="n">
-        <v>1.9103</v>
+        <v>0.6179</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3288</v>
+        <v>-0.0922</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.6032</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>0.6032</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.2065</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>H. MORRO BALERA</t>
+          <t>C. POYATOS PARRA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.8324</v>
+        <v>-3.7261</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.8566</v>
+        <v>-2.476</v>
       </c>
       <c r="F23" t="n">
-        <v>0.0243</v>
+        <v>-1.2501</v>
       </c>
       <c r="G23" t="n">
-        <v>-3.2841</v>
+        <v>-3.752</v>
       </c>
       <c r="H23" t="n">
-        <v>0.2269</v>
+        <v>-2.2725</v>
       </c>
       <c r="I23" t="n">
-        <v>-3.511</v>
+        <v>-1.4795</v>
       </c>
       <c r="J23" t="n">
-        <v>-2.3579</v>
+        <v>-2.5748</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.3173</v>
+        <v>-2.0151</v>
       </c>
       <c r="L23" t="n">
-        <v>-2.0406</v>
+        <v>-0.5597</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.9263</v>
+        <v>-1.1772</v>
       </c>
       <c r="N23" t="n">
-        <v>0.5442</v>
+        <v>-0.2574</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.4704</v>
+        <v>-0.9198</v>
       </c>
       <c r="P23" t="n">
-        <v>0.7935</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>-1.1903</v>
       </c>
       <c r="R23" t="n">
-        <v>0.7935</v>
+        <v>1.1903</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.3418</v>
+        <v>0.6292</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.4988</v>
+        <v>0.6859</v>
       </c>
       <c r="U23" t="n">
-        <v>0.157</v>
+        <v>-0.0567</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>-0.6032</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>0.6032</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.7727</v>
+        <v>-4.5722</v>
       </c>
       <c r="E24" t="n">
-        <v>-5.8003</v>
+        <v>-4.984</v>
       </c>
       <c r="F24" t="n">
-        <v>0.0276</v>
+        <v>0.4119</v>
       </c>
       <c r="G24" t="n">
         <v>-2.7758</v>
@@ -2326,13 +2326,13 @@
         <v>1.7855</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.3503</v>
+        <v>0.8502999999999999</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.09619999999999999</v>
+        <v>0.72</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.254</v>
+        <v>0.1303</v>
       </c>
       <c r="V24" t="n">
         <v>-0.266</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-7.1115</v>
+        <v>-5.6746</v>
       </c>
       <c r="E25" t="n">
-        <v>-5.0169</v>
+        <v>-3.9966</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.0946</v>
+        <v>-1.678</v>
       </c>
       <c r="G25" t="n">
         <v>-7.1763</v>
@@ -2404,13 +2404,13 @@
         <v>1.3887</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.7368</v>
+        <v>0.7000999999999999</v>
       </c>
       <c r="T25" t="n">
-        <v>0.0284</v>
+        <v>1.0487</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.7652</v>
+        <v>-0.3486</v>
       </c>
       <c r="V25" t="n">
         <v>0.6032</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-18.6518</v>
+        <v>-16.6114</v>
       </c>
       <c r="E26" t="n">
-        <v>-11.5328</v>
+        <v>-11.5329</v>
       </c>
       <c r="F26" t="n">
-        <v>-7.119</v>
+        <v>-5.0786</v>
       </c>
       <c r="G26" t="n">
         <v>-25.7253</v>
@@ -2458,7 +2458,7 @@
         <v>-6.5772</v>
       </c>
       <c r="K26" t="n">
-        <v>-6.317100000000001</v>
+        <v>-6.3171</v>
       </c>
       <c r="L26" t="n">
         <v>-0.2601</v>
@@ -2482,13 +2482,13 @@
         <v>16.8626</v>
       </c>
       <c r="S26" t="n">
-        <v>5.725200000000001</v>
+        <v>7.765999999999999</v>
       </c>
       <c r="T26" t="n">
-        <v>7.0296</v>
+        <v>7.0295</v>
       </c>
       <c r="U26" t="n">
-        <v>-1.3043</v>
+        <v>0.7363999999999999</v>
       </c>
       <c r="V26" t="n">
         <v>0.3564000000000001</v>
